--- a/Others/03_Gold STTM/sttm_silver_to_gold.xlsx
+++ b/Others/03_Gold STTM/sttm_silver_to_gold.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vscode\adf_project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955CFBC1-845E-4BF3-BAAB-4FE97ECDB6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{955CFBC1-845E-4BF3-BAAB-4FE97ECDB6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3728083-9518-48CE-B39A-C80C6E0F51B6}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,23 @@
     <sheet name="hospital_daily_summary" sheetId="3" r:id="rId3"/>
     <sheet name="lab_test_trends" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -28,7 +44,7 @@
     <t>Source-to-Target Mapping (STTM)</t>
   </si>
   <si>
-    <t>Silver → Gold  |  CareSync Health Network</t>
+    <t>Silver → Gold  |  QNXT Health Network</t>
   </si>
   <si>
     <t>Document Information</t>
@@ -37,7 +53,7 @@
     <t>Document Title</t>
   </si>
   <si>
-    <t>STTM — Silver to Gold (CareSync Health Network)</t>
+    <t>STTM — Silver to Gold (QNXT Health Network)</t>
   </si>
   <si>
     <t>Scope</t>
@@ -569,7 +585,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -663,7 +679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -677,20 +693,21 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -994,275 +1011,310 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="4" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="9" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" spans="1:6" ht="8.1" customHeight="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" ht="22.15" customHeight="1">
+      <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+    </row>
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" spans="1:6" ht="27.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" spans="1:6" ht="27.4" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="10" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="9" t="s">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+    </row>
+    <row r="10" spans="1:6" ht="22.15" customHeight="1">
+      <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="20" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="9" t="s">
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+    </row>
+    <row r="20" spans="1:6" ht="22.15" customHeight="1">
+      <c r="A20" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" ht="30" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" ht="30" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" ht="30" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="1:6" ht="30" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="9" t="s">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="29" spans="1:6" ht="22.15" customHeight="1">
+      <c r="A29" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
@@ -1272,8 +1324,11 @@
       <c r="C30" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:6" ht="30" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>47</v>
       </c>
@@ -1283,8 +1338,11 @@
       <c r="C31" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="1:6" ht="30" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>49</v>
       </c>
@@ -1294,8 +1352,11 @@
       <c r="C32" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="1:3" ht="30" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>52</v>
       </c>
@@ -1308,6 +1369,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="A1:F1"/>
@@ -1324,8 +1387,6 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1334,7 +1395,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1343,112 +1404,118 @@
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:5" ht="28.15" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="3" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="9" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" ht="6" customHeight="1">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" ht="22.15" customHeight="1">
+      <c r="A3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" spans="1:5" ht="34.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:5" ht="34.15" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="12" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="9" t="s">
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+    </row>
+    <row r="12" spans="1:5" ht="22.15" customHeight="1">
+      <c r="A12" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>66</v>
       </c>
@@ -1465,7 +1532,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" ht="30" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>71</v>
       </c>
@@ -1482,7 +1549,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="30" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>76</v>
       </c>
@@ -1497,7 +1564,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" ht="30" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>79</v>
       </c>
@@ -1512,7 +1579,7 @@
       </c>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" ht="30" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>81</v>
       </c>
@@ -1527,7 +1594,7 @@
       </c>
       <c r="E17" s="4"/>
     </row>
-    <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" ht="30" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>84</v>
       </c>
@@ -1544,7 +1611,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" ht="30" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>87</v>
       </c>
@@ -1559,7 +1626,7 @@
       </c>
       <c r="E19" s="4"/>
     </row>
-    <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" ht="30" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>89</v>
       </c>
@@ -1576,7 +1643,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" ht="30" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>92</v>
       </c>
@@ -1593,7 +1660,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>95</v>
       </c>
@@ -1608,7 +1675,7 @@
       </c>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" ht="30" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>98</v>
       </c>
@@ -1623,7 +1690,7 @@
       </c>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" ht="30" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>101</v>
       </c>
@@ -1638,7 +1705,7 @@
       </c>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" ht="30" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>103</v>
       </c>
@@ -1653,7 +1720,7 @@
       </c>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" ht="30" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>105</v>
       </c>
@@ -1668,7 +1735,7 @@
       </c>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" ht="30" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>108</v>
       </c>
@@ -1683,7 +1750,7 @@
       </c>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" ht="30" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>111</v>
       </c>
@@ -1698,7 +1765,7 @@
       </c>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" ht="30" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>113</v>
       </c>
@@ -1715,16 +1782,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1733,7 +1800,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1742,123 +1809,129 @@
     <col min="5" max="5" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:5" ht="28.15" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="3" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="9" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" ht="6" customHeight="1">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" ht="22.15" customHeight="1">
+      <c r="A3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-    </row>
-    <row r="13" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="13" spans="1:5" ht="22.15" customHeight="1">
+      <c r="A13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>66</v>
       </c>
@@ -1875,7 +1948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="30" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>95</v>
       </c>
@@ -1890,7 +1963,7 @@
       </c>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" ht="30" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>98</v>
       </c>
@@ -1905,7 +1978,7 @@
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" ht="30" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>125</v>
       </c>
@@ -1920,7 +1993,7 @@
       </c>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" ht="30" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>126</v>
       </c>
@@ -1937,7 +2010,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" ht="30" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>130</v>
       </c>
@@ -1952,7 +2025,7 @@
       </c>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" ht="30" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>105</v>
       </c>
@@ -1967,7 +2040,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" ht="30" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>134</v>
       </c>
@@ -1982,7 +2055,7 @@
       </c>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>137</v>
       </c>
@@ -1997,7 +2070,7 @@
       </c>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" ht="30" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>108</v>
       </c>
@@ -2012,7 +2085,7 @@
       </c>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" ht="30" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>111</v>
       </c>
@@ -2027,7 +2100,7 @@
       </c>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" ht="30" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>142</v>
       </c>
@@ -2042,7 +2115,7 @@
       </c>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" ht="30" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>146</v>
       </c>
@@ -2057,7 +2130,7 @@
       </c>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" ht="30" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>148</v>
       </c>
@@ -2074,7 +2147,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" ht="30" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>151</v>
       </c>
@@ -2112,7 +2185,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2121,123 +2194,129 @@
     <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:5" ht="28.15" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="3" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="9" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" ht="6" customHeight="1">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" ht="22.15" customHeight="1">
+      <c r="A3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:5" ht="31.5" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-    </row>
-    <row r="13" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="13" spans="1:5" ht="22.15" customHeight="1">
+      <c r="A13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>66</v>
       </c>
@@ -2254,7 +2333,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="30" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>160</v>
       </c>
@@ -2269,7 +2348,7 @@
       </c>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" ht="30" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>162</v>
       </c>
@@ -2284,7 +2363,7 @@
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" ht="30" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>164</v>
       </c>
@@ -2299,7 +2378,7 @@
       </c>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" ht="30" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>166</v>
       </c>
@@ -2316,7 +2395,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" ht="30" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>170</v>
       </c>
@@ -2333,7 +2412,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" ht="30" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>105</v>
       </c>
@@ -2348,7 +2427,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" ht="30" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>108</v>
       </c>
@@ -2363,7 +2442,7 @@
       </c>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>111</v>
       </c>
@@ -2378,7 +2457,7 @@
       </c>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" ht="30" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>142</v>
       </c>
@@ -2393,7 +2472,7 @@
       </c>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" ht="30" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>146</v>
       </c>
@@ -2408,7 +2487,7 @@
       </c>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" ht="30" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>174</v>
       </c>
@@ -2425,7 +2504,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" ht="30" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>177</v>
       </c>
